--- a/AAII_Financials/Yearly/HBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HBI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>HBI</t>
   </si>
@@ -656,199 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44562</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44198</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43827</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43463</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43099</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42371</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42007</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41636</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41272</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5636500</v>
+      </c>
+      <c r="E8" s="3">
         <v>6233700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6801200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6127200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6425700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6804000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6471400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6028200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5731500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5324700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4627800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4525700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4434300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3668000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3995500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4139400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3853800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3971400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4112400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3784100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3752200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3595200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3420300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3016100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3105700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2941100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1968600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2238100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2661800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2273300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2454300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2691600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2687400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2276000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2136300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1904400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1611700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1420000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1493200</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -865,50 +877,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E12" s="3">
         <v>38900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>39300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>37400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>41800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>59300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>65500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>70100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>62300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>63300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>51300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>48300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>47100</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -948,32 +964,35 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E14" s="3">
         <v>59900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>184700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>831000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>126000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>80200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>326800</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -987,12 +1006,15 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1032,9 +1054,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1048,92 +1073,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5354800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5714100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6049200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6084500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5575000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5939300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5728200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5252600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5136400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4760800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4112600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4085600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3987200</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>281700</v>
+      </c>
+      <c r="E18" s="3">
         <v>519500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>752000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>42700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>850700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>864700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>743200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>775600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>595100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>564000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>515200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>440100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>447100</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1150,92 +1182,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-306800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-166800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-171000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-184900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-207100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-221100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-214100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-204400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-121200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-99000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-119400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-177200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-162600</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E21" s="3">
         <v>459000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>695300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>774500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>775400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>651600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>674400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>577800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>563200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>486700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>356000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>375300</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1275,93 +1314,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E23" s="3">
         <v>352700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>581100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-142200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>643600</v>
       </c>
       <c r="H23" s="3">
         <v>643600</v>
       </c>
       <c r="I23" s="3">
+        <v>643600</v>
+      </c>
+      <c r="J23" s="3">
         <v>529100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>571200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>473900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>465000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>395800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>262900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>284600</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E24" s="3">
         <v>483900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>64800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-71600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>70200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>106800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>453100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>34300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>45000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>60400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>30500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>42000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1401,93 +1449,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-131200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>516300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-70600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>573300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>536700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>76000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>536900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>428900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>404500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>330500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>232400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>242600</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-131200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>516300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-70600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>573300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>536700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>76000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>536900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>428900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>404500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>330500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>232400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>242600</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1527,51 +1584,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>4000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-439100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-5000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>27400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>2900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-459100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>2500</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-67800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>24100</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1611,9 +1674,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1653,93 +1719,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>306800</v>
+      </c>
+      <c r="E32" s="3">
         <v>166800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>171000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>184900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>207100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>221100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>214100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>204400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>121200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>99000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>119400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>177200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>162600</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-127200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>77200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-75600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>600700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>539700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-383100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>539400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>428900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>404500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>330500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>164700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>266700</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1779,98 +1854,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-127200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>77200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-75600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>600700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>539700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-383100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>539400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>428900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>404500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>330500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>164700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>266700</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44562</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44198</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43827</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43463</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43099</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42371</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42007</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41636</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41272</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1887,8 +1971,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1905,50 +1990,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>205500</v>
+      </c>
+      <c r="E41" s="3">
         <v>238400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>536300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>900600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>328900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>433000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>421600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>460200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>319200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>239900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>115900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1961,204 +2050,219 @@
       <c r="F42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="3">
         <v>900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3000</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>557700</v>
+      </c>
+      <c r="E43" s="3">
         <v>721400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>894200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>768200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>815200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>870900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>903300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>836900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>680400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>672000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>578600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>506300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>470700</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1368000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1979700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1584000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1367800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1905800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2056800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1875000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1840600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1814600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1537200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1283300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1253100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1607600</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E45" s="3">
         <v>192300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>513700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>392800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>173700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>169000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>186400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>179100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>102200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>313200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>265900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>225300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>217200</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2276200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3131800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3528100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3429400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3224600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3542100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3386400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3321200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2917900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2550200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2243700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2027500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2330800</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2171,14 +2275,14 @@
       <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3">
         <v>5300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12400</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>10</v>
@@ -2192,99 +2296,108 @@
       <c r="M47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>843300</v>
+      </c>
+      <c r="E48" s="3">
         <v>857300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>805300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>910500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1075700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>609800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>624000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1384900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1300900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1348800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>579900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>596200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>635400</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2348400</v>
+      </c>
+      <c r="E49" s="3">
         <v>2364600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2353300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2452800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2756500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2797100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2569900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3669500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2235300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2105500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1004100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>553400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>603100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2324,9 +2437,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2366,51 +2482,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>172400</v>
+      </c>
+      <c r="E52" s="3">
         <v>150200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>384800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>927300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>291900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>362800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>314600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>532900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>494400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>642800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>262400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>454600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>465400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2450,51 +2572,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5640300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6503900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7071400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7719900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7354000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7238200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6894800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6930500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5597600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5208200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4090000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3631700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4034700</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2511,8 +2639,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2529,260 +2658,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>736300</v>
+      </c>
+      <c r="E57" s="3">
         <v>917500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1214800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>891900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>959000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1029900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>867600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>761600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>673000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>621200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>466300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>403600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>451500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E58" s="3">
         <v>247000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>25000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>263900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>115200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>446400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>261500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>234800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>370600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>369800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>218000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>200100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>230000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>589300</v>
+      </c>
+      <c r="E59" s="3">
         <v>626100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1087200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1711900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>697300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>569600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>649600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>629300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>920700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>987100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>315000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>272000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>252200</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1390600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1790600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2327100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2124400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1771400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2045900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1778700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1625700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1503900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1482400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>999300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>875700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>933700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3235600</v>
+      </c>
+      <c r="E61" s="3">
         <v>3612100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3326100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3739400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3256900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3534200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3702100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3507700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2232700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1614000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1467000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1317500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1807800</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>594800</v>
+      </c>
+      <c r="E62" s="3">
         <v>702900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>715800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>929100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1089100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>886600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>727800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>573200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>585100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>725000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>393100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>551700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>612100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2822,9 +2970,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2864,9 +3015,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2906,51 +3060,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5221000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6105600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6368900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6905900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6117400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6366100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6208600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5706600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4321700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3821400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2859400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2744800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3353600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2967,8 +3127,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3008,9 +3169,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3050,9 +3214,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3092,9 +3259,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3134,51 +3304,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>554800</v>
+      </c>
+      <c r="E72" s="3">
         <v>572100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>935300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1069500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1546200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1079500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>850300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1396100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1389300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1464400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1181400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>911500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>746800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3218,9 +3394,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3260,9 +3439,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3302,51 +3484,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>419400</v>
+      </c>
+      <c r="E76" s="3">
         <v>398300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>702500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>814000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1236600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>872100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>686200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1223900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1275900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1386800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1230600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>886900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>681100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3386,98 +3574,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44562</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44198</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43827</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43463</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43099</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42371</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42007</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41636</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41272</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-127200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>77200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-75600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>600700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>539700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-383100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>539400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>428900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>404500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>330500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>164700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>266700</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3494,50 +3691,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E83" s="3">
         <v>106300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>114200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>132400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>131000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>131800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>122500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>103200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>103900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>98200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>90900</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>90700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3577,9 +3778,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3619,9 +3823,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3661,9 +3868,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3703,9 +3913,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3745,51 +3958,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>561700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-358800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>623400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>448500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>803400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>643400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>655700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>605600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>227000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>508100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>591300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>553600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>173500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3806,50 +4025,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-112100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-69300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-53700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-101100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-86300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-87000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-83400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-99400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-64300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-43600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-90100</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3889,9 +4112,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3931,51 +4157,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-216400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-52500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-109700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-418700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-104500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-966600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-276800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-358300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-597400</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-85600</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3992,50 +4224,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-209300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-209500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-210400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-217000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-216300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-219900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-167400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-161300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-119600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-59400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4075,9 +4311,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4117,9 +4356,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4159,133 +4401,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-580100</v>
+      </c>
+      <c r="E100" s="3">
         <v>295800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-888000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>142200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-824000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-585800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>511100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>133000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-23800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>93800</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-95000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-42800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-32900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>31100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14600</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1100</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-322200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-350000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>580700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-125800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>141100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>79300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>124000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>73100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8300</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>HBI</t>
   </si>
@@ -775,10 +775,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3668000</v>
+        <v>3691300</v>
       </c>
       <c r="E9" s="3">
-        <v>3995500</v>
+        <v>3981300</v>
       </c>
       <c r="F9" s="3">
         <v>4139400</v>
@@ -787,13 +787,13 @@
         <v>3853800</v>
       </c>
       <c r="H9" s="3">
-        <v>3971400</v>
+        <v>3939600</v>
       </c>
       <c r="I9" s="3">
         <v>4112400</v>
       </c>
       <c r="J9" s="3">
-        <v>3784100</v>
+        <v>3927000</v>
       </c>
       <c r="K9" s="3">
         <v>3752200</v>
@@ -820,10 +820,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1968600</v>
+        <v>1945200</v>
       </c>
       <c r="E10" s="3">
-        <v>2238100</v>
+        <v>2252300</v>
       </c>
       <c r="F10" s="3">
         <v>2661800</v>
@@ -832,13 +832,13 @@
         <v>2273300</v>
       </c>
       <c r="H10" s="3">
-        <v>2454300</v>
+        <v>2486200</v>
       </c>
       <c r="I10" s="3">
         <v>2691600</v>
       </c>
       <c r="J10" s="3">
-        <v>2687400</v>
+        <v>2544400</v>
       </c>
       <c r="K10" s="3">
         <v>2276000</v>
@@ -974,25 +974,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>123000</v>
+        <v>99100</v>
       </c>
       <c r="E14" s="3">
-        <v>59900</v>
+        <v>75300</v>
       </c>
       <c r="F14" s="3">
-        <v>184700</v>
+        <v>177400</v>
       </c>
       <c r="G14" s="3">
-        <v>831000</v>
+        <v>734200</v>
       </c>
       <c r="H14" s="3">
-        <v>126000</v>
+        <v>62500</v>
       </c>
       <c r="I14" s="3">
         <v>80200</v>
       </c>
       <c r="J14" s="3">
-        <v>326800</v>
+        <v>198300</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1019,25 +1019,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>106300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>114200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>132400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>131000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>131800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>122500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,25 +1080,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5354800</v>
+        <v>5273400</v>
       </c>
       <c r="E17" s="3">
-        <v>5714100</v>
+        <v>5639300</v>
       </c>
       <c r="F17" s="3">
-        <v>6049200</v>
+        <v>5888100</v>
       </c>
       <c r="G17" s="3">
-        <v>6084500</v>
+        <v>5370500</v>
       </c>
       <c r="H17" s="3">
-        <v>5575000</v>
+        <v>5532500</v>
       </c>
       <c r="I17" s="3">
-        <v>5939300</v>
+        <v>5879500</v>
       </c>
       <c r="J17" s="3">
-        <v>5728200</v>
+        <v>5563500</v>
       </c>
       <c r="K17" s="3">
         <v>5252600</v>
@@ -1125,25 +1125,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>281700</v>
+        <v>363100</v>
       </c>
       <c r="E18" s="3">
-        <v>519500</v>
+        <v>594300</v>
       </c>
       <c r="F18" s="3">
-        <v>752000</v>
+        <v>913100</v>
       </c>
       <c r="G18" s="3">
-        <v>42700</v>
+        <v>756600</v>
       </c>
       <c r="H18" s="3">
-        <v>850700</v>
+        <v>893200</v>
       </c>
       <c r="I18" s="3">
-        <v>864700</v>
+        <v>924400</v>
       </c>
       <c r="J18" s="3">
-        <v>743200</v>
+        <v>907900</v>
       </c>
       <c r="K18" s="3">
         <v>775600</v>
@@ -1189,25 +1189,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-306800</v>
+        <v>11000</v>
       </c>
       <c r="E20" s="3">
-        <v>-166800</v>
+        <v>6800</v>
       </c>
       <c r="F20" s="3">
-        <v>-171000</v>
+        <v>-12200</v>
       </c>
       <c r="G20" s="3">
-        <v>-184900</v>
+        <v>-7200</v>
       </c>
       <c r="H20" s="3">
-        <v>-207100</v>
+        <v>6600</v>
       </c>
       <c r="I20" s="3">
-        <v>-221100</v>
+        <v>6000</v>
       </c>
       <c r="J20" s="3">
-        <v>-214100</v>
+        <v>6100</v>
       </c>
       <c r="K20" s="3">
         <v>-204400</v>
@@ -1234,25 +1234,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>79900</v>
+        <v>457100</v>
       </c>
       <c r="E21" s="3">
-        <v>459000</v>
+        <v>693800</v>
       </c>
       <c r="F21" s="3">
-        <v>695300</v>
+        <v>1039600</v>
       </c>
       <c r="G21" s="3">
-        <v>-9800</v>
+        <v>896300</v>
       </c>
       <c r="H21" s="3">
-        <v>774500</v>
+        <v>1017600</v>
       </c>
       <c r="I21" s="3">
-        <v>775400</v>
+        <v>1050200</v>
       </c>
       <c r="J21" s="3">
-        <v>651600</v>
+        <v>1024300</v>
       </c>
       <c r="K21" s="3">
         <v>674400</v>
@@ -1279,25 +1279,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>278100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>159500</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>166900</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>171900</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>180500</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>194700</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>174400</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1375,16 +1375,16 @@
         <v>483900</v>
       </c>
       <c r="F24" s="3">
-        <v>64800</v>
+        <v>60100</v>
       </c>
       <c r="G24" s="3">
-        <v>-71600</v>
+        <v>-109900</v>
       </c>
       <c r="H24" s="3">
         <v>70200</v>
       </c>
       <c r="I24" s="3">
-        <v>106800</v>
+        <v>103900</v>
       </c>
       <c r="J24" s="3">
         <v>453100</v>
@@ -1465,16 +1465,16 @@
         <v>-131200</v>
       </c>
       <c r="F26" s="3">
-        <v>516300</v>
+        <v>521000</v>
       </c>
       <c r="G26" s="3">
-        <v>-70600</v>
+        <v>-32300</v>
       </c>
       <c r="H26" s="3">
         <v>573300</v>
       </c>
       <c r="I26" s="3">
-        <v>536700</v>
+        <v>539700</v>
       </c>
       <c r="J26" s="3">
         <v>76000</v>
@@ -1507,22 +1507,22 @@
         <v>-17700</v>
       </c>
       <c r="E27" s="3">
-        <v>-131200</v>
+        <v>-127200</v>
       </c>
       <c r="F27" s="3">
-        <v>516300</v>
+        <v>77200</v>
       </c>
       <c r="G27" s="3">
-        <v>-70600</v>
+        <v>-75600</v>
       </c>
       <c r="H27" s="3">
-        <v>573300</v>
+        <v>600700</v>
       </c>
       <c r="I27" s="3">
-        <v>536700</v>
+        <v>539700</v>
       </c>
       <c r="J27" s="3">
-        <v>76000</v>
+        <v>73900</v>
       </c>
       <c r="K27" s="3">
         <v>536900</v>
@@ -1600,19 +1600,19 @@
         <v>4000</v>
       </c>
       <c r="F29" s="3">
-        <v>-439100</v>
+        <v>-443700</v>
       </c>
       <c r="G29" s="3">
-        <v>-5000</v>
+        <v>-43300</v>
       </c>
       <c r="H29" s="3">
         <v>27400</v>
       </c>
       <c r="I29" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-459100</v>
+        <v>-2100</v>
       </c>
       <c r="K29" s="3">
         <v>2500</v>
@@ -1729,25 +1729,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>306800</v>
+        <v>-11000</v>
       </c>
       <c r="E32" s="3">
-        <v>166800</v>
+        <v>-6800</v>
       </c>
       <c r="F32" s="3">
-        <v>171000</v>
+        <v>12200</v>
       </c>
       <c r="G32" s="3">
-        <v>184900</v>
+        <v>7200</v>
       </c>
       <c r="H32" s="3">
-        <v>207100</v>
+        <v>-6600</v>
       </c>
       <c r="I32" s="3">
-        <v>221100</v>
+        <v>-6000</v>
       </c>
       <c r="J32" s="3">
-        <v>214100</v>
+        <v>-6100</v>
       </c>
       <c r="K32" s="3">
         <v>204400</v>
@@ -1792,7 +1792,7 @@
         <v>539700</v>
       </c>
       <c r="J33" s="3">
-        <v>-383100</v>
+        <v>73900</v>
       </c>
       <c r="K33" s="3">
         <v>539400</v>
@@ -1882,7 +1882,7 @@
         <v>539700</v>
       </c>
       <c r="J35" s="3">
-        <v>-383100</v>
+        <v>73900</v>
       </c>
       <c r="K35" s="3">
         <v>539400</v>
@@ -2041,26 +2041,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>12400</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>4400</v>
@@ -2177,7 +2177,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>145000</v>
+        <v>144900</v>
       </c>
       <c r="E45" s="3">
         <v>192300</v>
@@ -2186,16 +2186,16 @@
         <v>513700</v>
       </c>
       <c r="G45" s="3">
-        <v>392800</v>
+        <v>391600</v>
       </c>
       <c r="H45" s="3">
-        <v>173700</v>
+        <v>173600</v>
       </c>
       <c r="I45" s="3">
-        <v>169000</v>
+        <v>158700</v>
       </c>
       <c r="J45" s="3">
-        <v>186400</v>
+        <v>186500</v>
       </c>
       <c r="K45" s="3">
         <v>179100</v>
@@ -2278,11 +2278,11 @@
       <c r="G47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>12400</v>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>1075700</v>
       </c>
       <c r="I48" s="3">
-        <v>609800</v>
+        <v>607700</v>
       </c>
       <c r="J48" s="3">
         <v>624000</v>
@@ -2357,10 +2357,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2348400</v>
+        <v>2442900</v>
       </c>
       <c r="E49" s="3">
-        <v>2364600</v>
+        <v>2418200</v>
       </c>
       <c r="F49" s="3">
         <v>2353300</v>
@@ -2492,25 +2492,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>172400</v>
+        <v>49400</v>
       </c>
       <c r="E52" s="3">
-        <v>150200</v>
+        <v>76400</v>
       </c>
       <c r="F52" s="3">
-        <v>384800</v>
+        <v>57000</v>
       </c>
       <c r="G52" s="3">
-        <v>927300</v>
+        <v>559300</v>
       </c>
       <c r="H52" s="3">
-        <v>291900</v>
+        <v>93900</v>
       </c>
       <c r="I52" s="3">
-        <v>362800</v>
+        <v>83900</v>
       </c>
       <c r="J52" s="3">
-        <v>314600</v>
+        <v>79600</v>
       </c>
       <c r="K52" s="3">
         <v>532900</v>
@@ -2710,19 +2710,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>65000</v>
+        <v>175600</v>
       </c>
       <c r="E58" s="3">
-        <v>247000</v>
+        <v>361800</v>
       </c>
       <c r="F58" s="3">
-        <v>25000</v>
+        <v>134500</v>
       </c>
       <c r="G58" s="3">
-        <v>263900</v>
+        <v>400400</v>
       </c>
       <c r="H58" s="3">
-        <v>115200</v>
+        <v>281200</v>
       </c>
       <c r="I58" s="3">
         <v>446400</v>
@@ -2755,25 +2755,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>589300</v>
+        <v>229300</v>
       </c>
       <c r="E59" s="3">
-        <v>626100</v>
+        <v>241100</v>
       </c>
       <c r="F59" s="3">
-        <v>1087200</v>
+        <v>580300</v>
       </c>
       <c r="G59" s="3">
-        <v>1711900</v>
+        <v>538100</v>
       </c>
       <c r="H59" s="3">
-        <v>697300</v>
+        <v>208300</v>
       </c>
       <c r="I59" s="3">
-        <v>569600</v>
+        <v>273900</v>
       </c>
       <c r="J59" s="3">
-        <v>649600</v>
+        <v>345900</v>
       </c>
       <c r="K59" s="3">
         <v>629300</v>
@@ -2845,19 +2845,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3235600</v>
+        <v>3595600</v>
       </c>
       <c r="E61" s="3">
-        <v>3612100</v>
+        <v>3938700</v>
       </c>
       <c r="F61" s="3">
-        <v>3326100</v>
+        <v>3607900</v>
       </c>
       <c r="G61" s="3">
-        <v>3739400</v>
+        <v>4071000</v>
       </c>
       <c r="H61" s="3">
-        <v>3256900</v>
+        <v>3615200</v>
       </c>
       <c r="I61" s="3">
         <v>3534200</v>
@@ -2890,25 +2890,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>594800</v>
+        <v>130600</v>
       </c>
       <c r="E62" s="3">
-        <v>702900</v>
+        <v>260100</v>
       </c>
       <c r="F62" s="3">
-        <v>715800</v>
+        <v>185400</v>
       </c>
       <c r="G62" s="3">
-        <v>929100</v>
+        <v>329100</v>
       </c>
       <c r="H62" s="3">
-        <v>1089100</v>
+        <v>327300</v>
       </c>
       <c r="I62" s="3">
-        <v>886600</v>
+        <v>407000</v>
       </c>
       <c r="J62" s="3">
-        <v>727800</v>
+        <v>322500</v>
       </c>
       <c r="K62" s="3">
         <v>573200</v>
@@ -3652,7 +3652,7 @@
         <v>539700</v>
       </c>
       <c r="J81" s="3">
-        <v>-383100</v>
+        <v>73900</v>
       </c>
       <c r="K81" s="3">
         <v>539400</v>
@@ -3698,25 +3698,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>105000</v>
+        <v>88500</v>
       </c>
       <c r="E83" s="3">
-        <v>106300</v>
+        <v>88100</v>
       </c>
       <c r="F83" s="3">
-        <v>114200</v>
+        <v>93800</v>
       </c>
       <c r="G83" s="3">
-        <v>132400</v>
+        <v>107700</v>
       </c>
       <c r="H83" s="3">
-        <v>131000</v>
+        <v>106100</v>
       </c>
       <c r="I83" s="3">
-        <v>131800</v>
+        <v>106100</v>
       </c>
       <c r="J83" s="3">
-        <v>122500</v>
+        <v>87600</v>
       </c>
       <c r="K83" s="3">
         <v>103200</v>
@@ -4234,22 +4234,22 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-209300</v>
+        <v>209300</v>
       </c>
       <c r="F96" s="3">
-        <v>-209500</v>
+        <v>209500</v>
       </c>
       <c r="G96" s="3">
-        <v>-210400</v>
+        <v>210400</v>
       </c>
       <c r="H96" s="3">
-        <v>-217000</v>
+        <v>217000</v>
       </c>
       <c r="I96" s="3">
-        <v>-216300</v>
+        <v>216300</v>
       </c>
       <c r="J96" s="3">
-        <v>-219900</v>
+        <v>219900</v>
       </c>
       <c r="K96" s="3">
         <v>-167400</v>

--- a/AAII_Financials/Yearly/HBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HBI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>HBI</t>
   </si>
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44562</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44198</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43827</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43463</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43099</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42371</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42007</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41636</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41272</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5636500</v>
+        <v>3507400</v>
       </c>
       <c r="E8" s="3">
-        <v>6233700</v>
+        <v>3639400</v>
       </c>
       <c r="F8" s="3">
+        <v>3862800</v>
+      </c>
+      <c r="G8" s="3">
         <v>6801200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6127200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6425700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6804000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6471400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6028200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5731500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5324700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4627800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4525700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4434300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3691300</v>
+        <v>2056700</v>
       </c>
       <c r="E9" s="3">
-        <v>3981300</v>
+        <v>2368700</v>
       </c>
       <c r="F9" s="3">
+        <v>2488000</v>
+      </c>
+      <c r="G9" s="3">
         <v>4139400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3853800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3939600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4112400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3927000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3752200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3595200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3420300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3016100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3105700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2941100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1945200</v>
+        <v>1450700</v>
       </c>
       <c r="E10" s="3">
-        <v>2252300</v>
+        <v>1270700</v>
       </c>
       <c r="F10" s="3">
+        <v>1374800</v>
+      </c>
+      <c r="G10" s="3">
         <v>2661800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2273300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2486200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2691600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2544400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2276000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2136300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1904400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1611700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1420000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1493200</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,53 +890,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>36000</v>
+        <v>16000</v>
       </c>
       <c r="E12" s="3">
-        <v>38900</v>
+        <v>18400</v>
       </c>
       <c r="F12" s="3">
+        <v>20100</v>
+      </c>
+      <c r="G12" s="3">
         <v>39300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>37400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>41800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>59300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>65500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>70100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>62300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>63300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>51300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>48300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>47100</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -967,35 +983,38 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>99100</v>
+        <v>238600</v>
       </c>
       <c r="E14" s="3">
-        <v>75300</v>
+        <v>5900</v>
       </c>
       <c r="F14" s="3">
+        <v>70100</v>
+      </c>
+      <c r="G14" s="3">
         <v>177400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>734200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>62500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>80200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>198300</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
@@ -1009,39 +1028,42 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>105000</v>
+        <v>79100</v>
       </c>
       <c r="E15" s="3">
-        <v>106300</v>
+        <v>80000</v>
       </c>
       <c r="F15" s="3">
+        <v>79400</v>
+      </c>
+      <c r="G15" s="3">
         <v>114200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>132400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>131000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>131800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>122500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1057,9 +1079,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1074,98 +1099,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5273400</v>
+        <v>3075100</v>
       </c>
       <c r="E17" s="3">
-        <v>5639300</v>
+        <v>3359300</v>
       </c>
       <c r="F17" s="3">
+        <v>3484300</v>
+      </c>
+      <c r="G17" s="3">
         <v>5888100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5370500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5532500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5879500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5563500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5252600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5136400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4760800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4112600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4085600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3987200</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>363100</v>
+        <v>432400</v>
       </c>
       <c r="E18" s="3">
-        <v>594300</v>
+        <v>280100</v>
       </c>
       <c r="F18" s="3">
+        <v>378600</v>
+      </c>
+      <c r="G18" s="3">
         <v>913100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>756600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>893200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>924400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>907900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>775600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>595100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>564000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>515200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>440100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>447100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1183,125 +1215,132 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>11000</v>
+        <v>55200</v>
       </c>
       <c r="E20" s="3">
-        <v>6800</v>
+        <v>42900</v>
       </c>
       <c r="F20" s="3">
+        <v>47000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-12200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-204400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-121200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-99000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-119400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-177200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-162600</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>457100</v>
+        <v>456200</v>
       </c>
       <c r="E21" s="3">
-        <v>693800</v>
+        <v>317200</v>
       </c>
       <c r="F21" s="3">
+        <v>411000</v>
+      </c>
+      <c r="G21" s="3">
         <v>1039600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>896300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1017600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1050200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1024300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>674400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>577800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>563200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>486700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>356000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>375300</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>278100</v>
+        <v>195900</v>
       </c>
       <c r="E22" s="3">
-        <v>159500</v>
+        <v>217000</v>
       </c>
       <c r="F22" s="3">
+        <v>134200</v>
+      </c>
+      <c r="G22" s="3">
         <v>166900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>171900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>180500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>194700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>174400</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1317,99 +1356,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-25100</v>
+        <v>-57400</v>
       </c>
       <c r="E23" s="3">
-        <v>352700</v>
+        <v>14300</v>
       </c>
       <c r="F23" s="3">
+        <v>127300</v>
+      </c>
+      <c r="G23" s="3">
         <v>581100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-142200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>643600</v>
       </c>
       <c r="I23" s="3">
         <v>643600</v>
       </c>
       <c r="J23" s="3">
+        <v>643600</v>
+      </c>
+      <c r="K23" s="3">
         <v>529100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>571200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>473900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>465000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>395800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>262900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>284600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-7400</v>
+        <v>40600</v>
       </c>
       <c r="E24" s="3">
-        <v>483900</v>
+        <v>-14800</v>
       </c>
       <c r="F24" s="3">
+        <v>447900</v>
+      </c>
+      <c r="G24" s="3">
         <v>60100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-109900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>70200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>103900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>453100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>34300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>45000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>60400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>65300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>30500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>42000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1452,99 +1500,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-17700</v>
+        <v>-98000</v>
       </c>
       <c r="E26" s="3">
-        <v>-131200</v>
+        <v>29100</v>
       </c>
       <c r="F26" s="3">
+        <v>-320500</v>
+      </c>
+      <c r="G26" s="3">
         <v>521000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>573300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>539700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>76000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>536900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>428900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>404500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>330500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>232400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>242600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-320400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-127200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>77200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-75600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>600700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>539700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>73900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>536900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>428900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>404500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>330500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>232400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>242600</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1587,54 +1644,60 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-222400</v>
       </c>
       <c r="E29" s="3">
-        <v>4000</v>
+        <v>-46900</v>
       </c>
       <c r="F29" s="3">
+        <v>193300</v>
+      </c>
+      <c r="G29" s="3">
         <v>-443700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-43300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>27400</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-2100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>2500</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-67800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>24100</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1677,9 +1740,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1722,99 +1788,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-11000</v>
+        <v>-55200</v>
       </c>
       <c r="E32" s="3">
-        <v>-6800</v>
+        <v>-42900</v>
       </c>
       <c r="F32" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="G32" s="3">
         <v>12200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>204400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>121200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>99000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>119400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>177200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>162600</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-320400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-127200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>77200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-75600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>600700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>539700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>73900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>539400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>428900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>404500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>330500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>164700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>266700</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1857,104 +1932,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-320400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-127200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>77200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-75600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>600700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>539700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>73900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>539400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>428900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>404500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>330500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>164700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>266700</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44562</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44198</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43827</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43463</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43099</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42371</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42007</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41636</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41272</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1972,8 +2056,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1991,53 +2076,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>205500</v>
+        <v>214900</v>
       </c>
       <c r="E41" s="3">
+        <v>185200</v>
+      </c>
+      <c r="F41" s="3">
         <v>238400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>536300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>900600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>328900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>433000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>421600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>460200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>319200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>239900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>115900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2063,206 +2152,221 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>4400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3000</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>557700</v>
+        <v>376200</v>
       </c>
       <c r="E43" s="3">
+        <v>423700</v>
+      </c>
+      <c r="F43" s="3">
         <v>721400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>894200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>768200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>815200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>870900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>903300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>836900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>680400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>672000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>578600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>506300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>470700</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1368000</v>
+        <v>871000</v>
       </c>
       <c r="E44" s="3">
+        <v>956400</v>
+      </c>
+      <c r="F44" s="3">
         <v>1979700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1584000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1367800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1905800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2056800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1875000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1840600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1814600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1537200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1283300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1253100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1607600</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>144900</v>
+        <v>253300</v>
       </c>
       <c r="E45" s="3">
+        <v>710900</v>
+      </c>
+      <c r="F45" s="3">
         <v>192300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>513700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>391600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>173600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>158700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>186500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>179100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>102200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>313200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>265900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>225300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>217200</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1715400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2276200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3131800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3528100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3429400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3224600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3542100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3386400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3321200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2917900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2550200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2243700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2027500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2330800</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2299,105 +2403,114 @@
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>843300</v>
+        <v>411000</v>
       </c>
       <c r="E48" s="3">
+        <v>624800</v>
+      </c>
+      <c r="F48" s="3">
         <v>857300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>805300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>910500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1075700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>607700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>624000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1384900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1300900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1348800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>579900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>596200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>635400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2442900</v>
+        <v>1616800</v>
       </c>
       <c r="E49" s="3">
+        <v>1712700</v>
+      </c>
+      <c r="F49" s="3">
         <v>2418200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2353300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2452800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2756500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2797100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2569900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3669500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2235300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2105500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1004100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>553400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>603100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2440,9 +2553,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2485,54 +2601,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>49400</v>
+        <v>79800</v>
       </c>
       <c r="E52" s="3">
+        <v>1008400</v>
+      </c>
+      <c r="F52" s="3">
         <v>76400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>57000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>559300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>93900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>83900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>79600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>532900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>494400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>642800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>262400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>454600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>465400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2575,54 +2697,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3840900</v>
+      </c>
+      <c r="E54" s="3">
         <v>5640300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6503900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7071400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7719900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7354000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7238200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6894800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6930500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5597600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5208200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4090000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3631700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4034700</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2640,8 +2768,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2659,278 +2788,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>736300</v>
+        <v>593400</v>
       </c>
       <c r="E57" s="3">
+        <v>538800</v>
+      </c>
+      <c r="F57" s="3">
         <v>917500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1214800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>891900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>959000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1029900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>867600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>761600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>673000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>621200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>466300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>403600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>451500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>175600</v>
+        <v>159200</v>
       </c>
       <c r="E58" s="3">
+        <v>129500</v>
+      </c>
+      <c r="F58" s="3">
         <v>361800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>134500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>400400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>281200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>446400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>261500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>234800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>370600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>369800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>218000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>200100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>230000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>229300</v>
+        <v>221400</v>
       </c>
       <c r="E59" s="3">
+        <v>498400</v>
+      </c>
+      <c r="F59" s="3">
         <v>241100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>580300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>538100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>208300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>273900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>345900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>629300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>920700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>987100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>315000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>272000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>252200</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1248500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1390600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1790600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2327100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2124400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1771400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2045900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1778700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1625700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1503900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1482400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>999300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>875700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>933700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3595600</v>
+        <v>2392200</v>
       </c>
       <c r="E61" s="3">
+        <v>3477000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3938700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3607900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4071000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3615200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3534200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3702100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3507700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2232700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1614000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1467000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1317500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1807800</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>130600</v>
+        <v>100000</v>
       </c>
       <c r="E62" s="3">
+        <v>255200</v>
+      </c>
+      <c r="F62" s="3">
         <v>260100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>185400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>329100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>327300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>407000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>322500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>573200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>585100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>725000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>393100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>551700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>612100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,9 +3121,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3018,9 +3169,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3063,54 +3217,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3806900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5221000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6105600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6368900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6905900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6117400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6366100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6208600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5706600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4321700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3821400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2859400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2744800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3353600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3128,8 +3288,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3172,9 +3333,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3217,9 +3381,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3262,9 +3429,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3307,54 +3477,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>234500</v>
+      </c>
+      <c r="E72" s="3">
         <v>554800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>572100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>935300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1069500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1546200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1079500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>850300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1396100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1389300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1464400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1181400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>911500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>746800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3573,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3442,9 +3621,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3487,54 +3669,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E76" s="3">
         <v>419400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>398300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>702500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>814000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1236600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>872100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>686200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1223900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1275900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1386800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1230600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>886900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>681100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3577,104 +3765,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44562</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44198</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43827</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43463</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43099</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42371</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42007</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41636</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41272</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-320400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-127200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>77200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-75600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>600700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>539700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>73900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>539400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>428900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>404500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>330500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>164700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>266700</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3692,53 +3889,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>88500</v>
+        <v>72500</v>
       </c>
       <c r="E83" s="3">
-        <v>88100</v>
+        <v>74300</v>
       </c>
       <c r="F83" s="3">
+        <v>73100</v>
+      </c>
+      <c r="G83" s="3">
         <v>93800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>107700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>106100</v>
       </c>
       <c r="I83" s="3">
         <v>106100</v>
       </c>
       <c r="J83" s="3">
+        <v>106100</v>
+      </c>
+      <c r="K83" s="3">
         <v>87600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>103200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>103900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>98200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>90900</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>90700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3781,9 +3982,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3826,9 +4030,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3871,9 +4078,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,9 +4126,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3961,54 +4174,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>264200</v>
+      </c>
+      <c r="E89" s="3">
         <v>561700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-358800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>623400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>448500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>803400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>643400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>655700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>605600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>227000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>508100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>591300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>553600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>173500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4026,53 +4245,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-44100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-112100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-69300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-53700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-101100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-86300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-87000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-83400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-99400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-64300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-43600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-90100</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4115,9 +4338,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4160,54 +4386,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>813000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-216400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-52500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-41100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-109700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-418700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-104500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-966600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-276800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-358300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-597400</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-85600</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4225,8 +4457,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4234,44 +4467,47 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>209300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>209500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>210400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>217000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>216300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>219900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-167400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-161300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-119600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-59400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4314,9 +4550,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4359,9 +4598,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4404,142 +4646,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1046700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-580100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>295800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-888000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>142200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-824000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-585800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>511100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>133000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-23800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>93800</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E101" s="3">
         <v>8900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-42800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-32900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>31100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14600</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-32900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-322200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-350000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>580700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-125800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>34200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>141100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>79300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>124000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>73100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HBI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HBI_YR_FIN.xlsx
@@ -1106,13 +1106,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3075100</v>
+        <v>3109500</v>
       </c>
       <c r="E17" s="3">
-        <v>3359300</v>
+        <v>3391900</v>
       </c>
       <c r="F17" s="3">
-        <v>3484300</v>
+        <v>3525900</v>
       </c>
       <c r="G17" s="3">
         <v>5888100</v>
@@ -1154,13 +1154,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>432400</v>
+        <v>398000</v>
       </c>
       <c r="E18" s="3">
-        <v>280100</v>
+        <v>247500</v>
       </c>
       <c r="F18" s="3">
-        <v>378600</v>
+        <v>336900</v>
       </c>
       <c r="G18" s="3">
         <v>913100</v>
@@ -1222,13 +1222,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>55200</v>
+        <v>20800</v>
       </c>
       <c r="E20" s="3">
-        <v>42900</v>
+        <v>10200</v>
       </c>
       <c r="F20" s="3">
-        <v>47000</v>
+        <v>5400</v>
       </c>
       <c r="G20" s="3">
         <v>-12200</v>
@@ -1798,13 +1798,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-55200</v>
+        <v>-20800</v>
       </c>
       <c r="E32" s="3">
-        <v>-42900</v>
+        <v>-10200</v>
       </c>
       <c r="F32" s="3">
-        <v>-47000</v>
+        <v>-5400</v>
       </c>
       <c r="G32" s="3">
         <v>12200</v>
